--- a/Result_computational/full_test_data.xlsx
+++ b/Result_computational/full_test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uirabat-my.sharepoint.com/personal/clement_bamogo_uir_ac_ma/Documents/Bureau/PhD/Paper 1/Code/lef-paper/Result_computational/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="8_{2423F7B1-EE68-4FA2-A658-9DB2F0A4E065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0370C09D-EEA9-45BD-AF95-1A667FE8DC55}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="8_{2423F7B1-EE68-4FA2-A658-9DB2F0A4E065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1FDB23C-B657-4272-B9D2-AFCD08814B30}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gurobi" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="155">
   <si>
     <t>Instance</t>
   </si>
@@ -104,12 +104,6 @@
     <t>(5, 4, 10, 1)</t>
   </si>
   <si>
-    <t>(15, 20, 30, 1)</t>
-  </si>
-  <si>
-    <t>(25, 50, 70, 2)</t>
-  </si>
-  <si>
     <t>cost</t>
   </si>
   <si>
@@ -140,66 +134,6 @@
     <t>(600, 150, 200, 6)</t>
   </si>
   <si>
-    <t xml:space="preserve">1391373.85 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 66.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1379062.81 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 64.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1391912.52 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 61.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1377636.13 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 62.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1385332.03 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 67.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1382182.17 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 107.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1383508.53 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 151.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1396277.3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 73.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1385686.53 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 96.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1382200.2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 70.47</t>
-  </si>
-  <si>
     <t>1374550.09</t>
   </si>
   <si>
@@ -257,192 +191,6 @@
     <t>36.62</t>
   </si>
   <si>
-    <t xml:space="preserve">28554.02 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61403.82 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61405.36 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61403.75 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61405.42 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">192842.51 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192863.29 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192856.15 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">192873.7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">192846.42 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">192862.96 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">192859.38 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">192871.67 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">192857.02 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">192843.64 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">291071.32 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291120.05 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291012.58 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291648.96 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290984.21 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292019.85 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291152.18 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291170.7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291888.71 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291174.41 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">713618.18 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 26.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">713529.77 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 23.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">715011.18 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 24.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">713097.83 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 23.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">715080.19 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 23.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712744.02 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 24.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710722.04 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 25.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712948.75 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 22.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">719742.26 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 24.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712748.88 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 24.78</t>
-  </si>
-  <si>
     <t>28554.02</t>
   </si>
   <si>
@@ -749,58 +497,10 @@
     <t>3090.09</t>
   </si>
   <si>
-    <t xml:space="preserve">6172440.17 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1701.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6194876.19 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1643.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6175554.46 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1702.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6172118.75 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1850.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6164636.36 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1737.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6189842.1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1787.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6184008.4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1869.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6198492.93 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2659.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6163285.01 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2210.97</t>
+    <t>(20, 20, 30, 2)</t>
+  </si>
+  <si>
+    <t>(50, 80, 70, 3)</t>
   </si>
 </sst>
 </file>
@@ -971,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1006,9 +706,6 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1042,9 +739,6 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1062,11 +756,354 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="89">
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -2026,446 +2063,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -2808,7 +2405,8 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2817,12 +2415,6 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -2869,88 +2461,88 @@
   <autoFilter ref="A1:U13" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Instance" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="time_1" dataDxfId="70"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="time_2" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="time_3" dataDxfId="68"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="time_4" dataDxfId="67"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="time_5" dataDxfId="66"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="time_6" dataDxfId="65"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="time_7" dataDxfId="64"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="time_8" dataDxfId="63"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="time_9" dataDxfId="62"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="time_10" dataDxfId="61"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="cost_1" dataDxfId="60"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="cost_2" dataDxfId="59"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="cost_3" dataDxfId="58"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="cost_4" dataDxfId="57"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="cost_5" dataDxfId="56"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="cost_6" dataDxfId="55"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="cost_7" dataDxfId="54"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="cost_8" dataDxfId="53"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="cost_9" dataDxfId="52"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="cost_10" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="time_1" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="time_2" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="time_3" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="time_4" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="time_5" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="time_6" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="time_7" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="time_8" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="time_9" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="time_10" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="cost_1" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="cost_2" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="cost_3" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="cost_4" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="cost_5" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="cost_6" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="cost_7" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="cost_8" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="cost_9" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="cost_10" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tableau25" displayName="Tableau25" ref="A1:U13" totalsRowShown="0" headerRowDxfId="50" dataDxfId="48" headerRowBorderDxfId="49" tableBorderDxfId="47" totalsRowBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tableau25" displayName="Tableau25" ref="A1:U13" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
   <autoFilter ref="A1:U13" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Instance" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Instance" dataDxfId="65">
       <calculatedColumnFormula>gurobi!A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="time_1" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="time_2" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="time_3" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="time_4" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="time_5" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="time_6" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="time_7" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="time_8" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="time_9" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="time_10" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="cost_1" dataDxfId="34"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="cost_2" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="cost_3" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="cost_4" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="cost_5" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="cost_6" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="cost_7" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="cost_8" dataDxfId="27"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="cost_9" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="cost_10" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="time_1" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="time_2" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="time_3" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="time_4" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="time_5" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="time_6" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="time_7" dataDxfId="58"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="time_8" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="time_9" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="time_10" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0300-00000C000000}" name="cost_1" dataDxfId="54"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="cost_2" dataDxfId="53"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="cost_3" dataDxfId="52"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0300-00000F000000}" name="cost_4" dataDxfId="51"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="cost_5" dataDxfId="50"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="cost_6" dataDxfId="49"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="cost_7" dataDxfId="48"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="cost_8" dataDxfId="47"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="cost_9" dataDxfId="46"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="cost_10" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tableau24" displayName="Tableau24" ref="A1:U13" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tableau24" displayName="Tableau24" ref="A1:U13" totalsRowShown="0" headerRowDxfId="44" headerRowBorderDxfId="43" tableBorderDxfId="42" totalsRowBorderDxfId="41">
   <autoFilter ref="A1:U13" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Instance" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="time_1" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="time_2" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="time_3" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="time_4" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="time_5" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="time_6" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="time_7" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="time_8" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="time_9" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="time_10" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="cost_1" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="cost_2" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="cost_3" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="cost_4" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="cost_5" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="cost_6" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="cost_7" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0200-000013000000}" name="cost_8" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0200-000014000000}" name="cost_9" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0200-000015000000}" name="cost_10" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Instance" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="time_1" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="time_2" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="time_3" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="time_4" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="time_5" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="time_6" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="time_7" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="time_8" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="time_9" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="time_10" dataDxfId="30"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="cost_1" dataDxfId="29"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="cost_2" dataDxfId="28"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="cost_3" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="cost_4" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="cost_5" dataDxfId="25"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="cost_6" dataDxfId="24"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="cost_7" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0200-000013000000}" name="cost_8" dataDxfId="22"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0200-000014000000}" name="cost_9" dataDxfId="21"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0200-000015000000}" name="cost_10" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3257,7 +2849,7 @@
     <col min="16" max="23" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -3292,435 +2884,435 @@
         <v>10</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="14">
+      <c r="A2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="13">
         <v>0</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>0.02</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="13">
         <v>0</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="13">
         <v>0</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="13">
         <v>0.02</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="13">
         <v>0</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="13">
         <v>0.02</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
         <v>0</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="13">
         <v>0</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="13">
         <v>0</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="13">
         <v>28554.02</v>
       </c>
-      <c r="M2" s="15">
+      <c r="M2" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>0.03</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="13">
         <v>0.02</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>0.02</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>0.05</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>0.02</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>0.02</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>0.02</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>0.02</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>0.06</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>0.06</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="13">
         <v>61402.879999999997</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="14">
         <v>6.7000000000000002E-5</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="14">
+      <c r="A4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="13">
         <v>0.33</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="13">
         <v>0.3</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>0.33</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="13">
         <v>0.33</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>0.39</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>0.33</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>0.3</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>0.3</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>0.48</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="13">
         <v>192817.2</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="14">
         <v>9.8999999999999994E-5</v>
       </c>
       <c r="W4" s="6"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="A5" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="13">
         <v>3.03</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <v>2.86</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>2.84</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>2.89</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>2.72</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>2.8</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>2.83</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>3.06</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>2.67</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>2.92</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
         <v>290932.3</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="14">
         <v>4.8000000000000001E-5</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="14">
+      <c r="A6" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="13">
         <v>116.16</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <v>128.44999999999999</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>123.7</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <v>128.66</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <v>129.91</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <v>128.55000000000001</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>133.06</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>133.52000000000001</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>133.09</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>128.16999999999999</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="13">
         <v>710215.25</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="A7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="13">
         <v>646.80999999999995</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <v>678.86</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>748.56</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>710.08</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <v>977.73</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <v>1025.17</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>774.86</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>1030.7</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="13">
         <v>1053.55</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>513.23</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="13">
         <v>1374194.39</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="14">
         <v>1E-3</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="14">
+      <c r="A8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="13">
         <v>1672.39</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <v>1033.0899999999999</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>985.86</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>1017.84</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <v>1043.8900000000001</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <v>839.36</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>1958.77</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>732.67</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>745.95</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>782.64</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="13">
         <v>1907714.3</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="14">
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="P8" s="8"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="14">
+      <c r="A9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="13">
         <v>3980.02</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <v>1913.55</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>2101.44</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <v>3344.53</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="13">
         <v>2159.2199999999998</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <v>4236.3599999999997</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>2052.48</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>2674.78</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="13">
         <v>2802.53</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>1964.47</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="13">
         <v>2230454.0699999998</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="14">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="P9" s="8"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="B10" s="14">
+      <c r="A10" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="13">
         <v>6979.64</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="13">
         <v>8071.2</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>10467.879999999999</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <v>8208.31</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <v>5195.03</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <v>7207.39</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>6371.33</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>4532.47</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="13">
         <v>5503.8</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <v>4557.2</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="13">
         <v>3526470.86</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="14">
         <v>8.1000000000000004E-5</v>
       </c>
       <c r="P10" s="8"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="17"/>
+      <c r="A11" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="16"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="18"/>
+      <c r="A12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="17"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="21"/>
+      <c r="A13" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3809,792 +3401,796 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="str">
+      <c r="A2" s="21" t="str">
         <f>gurobi!A2</f>
         <v>(2, 2, 4, 1)</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="K2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="S2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="T2" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="U2" s="23" t="s">
-        <v>73</v>
+      <c r="B2" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="C2" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="D2" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="E2" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="F2" s="22">
+        <v>0</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0</v>
+      </c>
+      <c r="H2" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="I2" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="J2" s="22">
+        <v>0</v>
+      </c>
+      <c r="K2" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="L2" s="22">
+        <v>28554.02</v>
+      </c>
+      <c r="M2" s="22">
+        <v>28554.02</v>
+      </c>
+      <c r="N2" s="22">
+        <v>28554.02</v>
+      </c>
+      <c r="O2" s="22">
+        <v>28554.02</v>
+      </c>
+      <c r="P2" s="22">
+        <v>28554.02</v>
+      </c>
+      <c r="Q2" s="22">
+        <v>28554.02</v>
+      </c>
+      <c r="R2" s="22">
+        <v>28554.02</v>
+      </c>
+      <c r="S2" s="22">
+        <v>28554.02</v>
+      </c>
+      <c r="T2" s="22">
+        <v>28554.02</v>
+      </c>
+      <c r="U2" s="22">
+        <v>28554.02</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="str">
+      <c r="A3" s="21" t="str">
         <f>gurobi!A3</f>
         <v>(5, 4, 10, 1)</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="L3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="N3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="O3" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="P3" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="R3" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="S3" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="T3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="U3" s="23" t="s">
-        <v>82</v>
+      <c r="B3" s="22">
+        <v>0.06</v>
+      </c>
+      <c r="C3" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="D3" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="22">
+        <v>0.06</v>
+      </c>
+      <c r="F3" s="22">
+        <v>0.03</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="I3" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="J3" s="22">
+        <v>0.02</v>
+      </c>
+      <c r="K3" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="L3" s="22">
+        <v>61403.82</v>
+      </c>
+      <c r="M3" s="22">
+        <v>61405.36</v>
+      </c>
+      <c r="N3" s="22">
+        <v>61403.82</v>
+      </c>
+      <c r="O3" s="22">
+        <v>61403.75</v>
+      </c>
+      <c r="P3" s="22">
+        <v>61405.36</v>
+      </c>
+      <c r="Q3" s="22">
+        <v>61403.75</v>
+      </c>
+      <c r="R3" s="22">
+        <v>61405.36</v>
+      </c>
+      <c r="S3" s="22">
+        <v>61405.36</v>
+      </c>
+      <c r="T3" s="22">
+        <v>61403.82</v>
+      </c>
+      <c r="U3" s="22">
+        <v>61405.42</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="str">
+      <c r="A4" s="21" t="str">
         <f>gurobi!A4</f>
         <v>(10, 8, 20, 2)</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="H4" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="M4" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="N4" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="O4" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="P4" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q4" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="R4" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="S4" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="T4" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="U4" s="23" t="s">
-        <v>94</v>
+      <c r="B4" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="C4" s="22">
+        <v>0.23</v>
+      </c>
+      <c r="D4" s="22">
+        <v>0.23</v>
+      </c>
+      <c r="E4" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="H4" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="I4" s="22">
+        <v>0.23</v>
+      </c>
+      <c r="J4" s="22">
+        <v>0.23</v>
+      </c>
+      <c r="K4" s="22">
+        <v>0.23</v>
+      </c>
+      <c r="L4" s="22">
+        <v>192842.51</v>
+      </c>
+      <c r="M4" s="22">
+        <v>192863.29</v>
+      </c>
+      <c r="N4" s="22">
+        <v>192856.15</v>
+      </c>
+      <c r="O4" s="22">
+        <v>192873.7</v>
+      </c>
+      <c r="P4" s="22">
+        <v>192846.42</v>
+      </c>
+      <c r="Q4" s="22">
+        <v>192862.96</v>
+      </c>
+      <c r="R4" s="22">
+        <v>192859.38</v>
+      </c>
+      <c r="S4" s="22">
+        <v>192871.67</v>
+      </c>
+      <c r="T4" s="22">
+        <v>192857.02</v>
+      </c>
+      <c r="U4" s="22">
+        <v>192843.64</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="str">
+      <c r="A5" s="21" t="str">
         <f>gurobi!A5</f>
-        <v>(15, 20, 30, 1)</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="L5" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="N5" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="O5" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="P5" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q5" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="R5" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="S5" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="T5" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="U5" s="23" t="s">
-        <v>113</v>
+        <v>(20, 20, 30, 2)</v>
+      </c>
+      <c r="B5" s="22">
+        <v>1.39</v>
+      </c>
+      <c r="C5" s="22">
+        <v>1.28</v>
+      </c>
+      <c r="D5" s="22">
+        <v>1.33</v>
+      </c>
+      <c r="E5" s="22">
+        <v>1.36</v>
+      </c>
+      <c r="F5" s="22">
+        <v>1.38</v>
+      </c>
+      <c r="G5" s="22">
+        <v>2.33</v>
+      </c>
+      <c r="H5" s="22">
+        <v>2.8</v>
+      </c>
+      <c r="I5" s="22">
+        <v>4.41</v>
+      </c>
+      <c r="J5" s="22">
+        <v>4.45</v>
+      </c>
+      <c r="K5" s="22">
+        <v>1.3</v>
+      </c>
+      <c r="L5" s="22">
+        <v>291071.32</v>
+      </c>
+      <c r="M5" s="22">
+        <v>291120.05</v>
+      </c>
+      <c r="N5" s="22">
+        <v>291012.58</v>
+      </c>
+      <c r="O5" s="22">
+        <v>291648.96000000002</v>
+      </c>
+      <c r="P5" s="22">
+        <v>290984.21000000002</v>
+      </c>
+      <c r="Q5" s="22">
+        <v>292019.84999999998</v>
+      </c>
+      <c r="R5" s="22">
+        <v>291152.18</v>
+      </c>
+      <c r="S5" s="22">
+        <v>291170.7</v>
+      </c>
+      <c r="T5" s="22">
+        <v>291888.71000000002</v>
+      </c>
+      <c r="U5" s="22">
+        <v>291174.40999999997</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="str">
+      <c r="A6" s="21" t="str">
         <f>gurobi!A6</f>
-        <v>(25, 50, 70, 2)</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="M6" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="N6" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="O6" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="P6" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q6" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="R6" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="S6" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="T6" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="U6" s="23" t="s">
-        <v>133</v>
+        <v>(50, 80, 70, 3)</v>
+      </c>
+      <c r="B6" s="22">
+        <v>26.2</v>
+      </c>
+      <c r="C6" s="22">
+        <v>23.84</v>
+      </c>
+      <c r="D6" s="22">
+        <v>24.14</v>
+      </c>
+      <c r="E6" s="22">
+        <v>23.59</v>
+      </c>
+      <c r="F6" s="22">
+        <v>23.22</v>
+      </c>
+      <c r="G6" s="22">
+        <v>24.38</v>
+      </c>
+      <c r="H6" s="22">
+        <v>25.05</v>
+      </c>
+      <c r="I6" s="22">
+        <v>22.03</v>
+      </c>
+      <c r="J6" s="22">
+        <v>24.17</v>
+      </c>
+      <c r="K6" s="22">
+        <v>24.78</v>
+      </c>
+      <c r="L6" s="22">
+        <v>713618.18</v>
+      </c>
+      <c r="M6" s="22">
+        <v>713529.77</v>
+      </c>
+      <c r="N6" s="22">
+        <v>715011.18</v>
+      </c>
+      <c r="O6" s="22">
+        <v>713097.83</v>
+      </c>
+      <c r="P6" s="22">
+        <v>715080.19</v>
+      </c>
+      <c r="Q6" s="22">
+        <v>712744.02</v>
+      </c>
+      <c r="R6" s="22">
+        <v>710722.04</v>
+      </c>
+      <c r="S6" s="22">
+        <v>712948.75</v>
+      </c>
+      <c r="T6" s="22">
+        <v>719742.26</v>
+      </c>
+      <c r="U6" s="22">
+        <v>712748.88</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="str">
+      <c r="A7" s="21" t="str">
         <f>gurobi!A7</f>
         <v>(70, 120, 100, 3)</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="N7" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="P7" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q7" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="R7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S7" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="T7" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="U7" s="23" t="s">
-        <v>52</v>
+      <c r="B7" s="22">
+        <v>66.06</v>
+      </c>
+      <c r="C7" s="22">
+        <v>64.16</v>
+      </c>
+      <c r="D7" s="22">
+        <v>61.56</v>
+      </c>
+      <c r="E7" s="22">
+        <v>62.5</v>
+      </c>
+      <c r="F7" s="22">
+        <v>67.33</v>
+      </c>
+      <c r="G7" s="22">
+        <v>107.95</v>
+      </c>
+      <c r="H7" s="22">
+        <v>151.34</v>
+      </c>
+      <c r="I7" s="22">
+        <v>73.53</v>
+      </c>
+      <c r="J7" s="22">
+        <v>96.17</v>
+      </c>
+      <c r="K7" s="22">
+        <v>70.47</v>
+      </c>
+      <c r="L7" s="22">
+        <v>1391373.85</v>
+      </c>
+      <c r="M7" s="22">
+        <v>1379062.81</v>
+      </c>
+      <c r="N7" s="22">
+        <v>1391912.52</v>
+      </c>
+      <c r="O7" s="22">
+        <v>1377636.13</v>
+      </c>
+      <c r="P7" s="22">
+        <v>1385332.03</v>
+      </c>
+      <c r="Q7" s="22">
+        <v>1382182.17</v>
+      </c>
+      <c r="R7" s="22">
+        <v>1383508.53</v>
+      </c>
+      <c r="S7" s="22">
+        <v>1396277.3</v>
+      </c>
+      <c r="T7" s="22">
+        <v>1385686.53</v>
+      </c>
+      <c r="U7" s="22">
+        <v>1382200.2</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="str">
+      <c r="A8" s="21" t="str">
         <f>gurobi!A8</f>
         <v>(100, 120, 100, 4)</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="22">
         <v>147.28</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="22">
         <v>157.41999999999999</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="22">
         <v>321.11</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <v>185.5</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="22">
         <v>209.78</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="22">
         <v>91.12</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="22">
         <v>102.78</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="22">
         <v>87.98</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="22">
         <v>97.47</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="22">
         <v>96.3</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="22">
         <v>1930534.2</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="22">
         <v>1924079.4</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="22">
         <v>1938449.08</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="22">
         <v>1920198.12</v>
       </c>
-      <c r="P8" s="23">
+      <c r="P8" s="22">
         <v>1931357.36</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="Q8" s="22">
         <v>1940309.87</v>
       </c>
-      <c r="R8" s="23">
+      <c r="R8" s="22">
         <v>1922098.53</v>
       </c>
-      <c r="S8" s="23">
+      <c r="S8" s="22">
         <v>1936385.15</v>
       </c>
-      <c r="T8" s="23">
+      <c r="T8" s="22">
         <v>1933345.24</v>
       </c>
-      <c r="U8" s="23">
+      <c r="U8" s="22">
         <v>1916915.82</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="str">
+      <c r="A9" s="21" t="str">
         <f>gurobi!A9</f>
         <v>(150, 120, 130, 4)</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="22">
         <v>159.25</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="22">
         <v>170.81</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="22">
         <v>172.03</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="22">
         <v>157.41999999999999</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="22">
         <v>173.16</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="22">
         <v>177.88</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="22">
         <v>163.41</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="22">
         <v>175.88</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="22">
         <v>172.84</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="22">
         <v>168.62</v>
       </c>
-      <c r="L9" s="23">
+      <c r="L9" s="22">
         <v>2239123.6</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="22">
         <v>2239103.19</v>
       </c>
-      <c r="N9" s="23">
+      <c r="N9" s="22">
         <v>2238557.35</v>
       </c>
-      <c r="O9" s="23">
+      <c r="O9" s="22">
         <v>2244165.2999999998</v>
       </c>
-      <c r="P9" s="23">
+      <c r="P9" s="22">
         <v>2234039.69</v>
       </c>
-      <c r="Q9" s="23">
+      <c r="Q9" s="22">
         <v>2238454.75</v>
       </c>
-      <c r="R9" s="23">
+      <c r="R9" s="22">
         <v>2241764.88</v>
       </c>
-      <c r="S9" s="23">
+      <c r="S9" s="22">
         <v>2237247.09</v>
       </c>
-      <c r="T9" s="23">
+      <c r="T9" s="22">
         <v>2245534.5099999998</v>
       </c>
-      <c r="U9" s="23">
+      <c r="U9" s="22">
         <v>2240536.41</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="str">
+      <c r="A10" s="21" t="str">
         <f>gurobi!A10</f>
         <v>(200, 130, 150, 5)</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="22">
         <v>347.72</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="22">
         <v>344.75</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="22">
         <v>360.97</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <v>369.77</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="22">
         <v>334.67</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="22">
         <v>356.69</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="22">
         <v>339.31</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="22">
         <v>339.95</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="22">
         <v>379.64</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="22">
         <v>341.94</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="22">
         <v>3560503.03</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="22">
         <v>3550802.09</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="22">
         <v>3558668.19</v>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="22">
         <v>3553207.48</v>
       </c>
-      <c r="P10" s="23">
+      <c r="P10" s="22">
         <v>3573568.13</v>
       </c>
-      <c r="Q10" s="23">
+      <c r="Q10" s="22">
         <v>3564513.48</v>
       </c>
-      <c r="R10" s="23">
+      <c r="R10" s="22">
         <v>3554218.58</v>
       </c>
-      <c r="S10" s="23">
+      <c r="S10" s="22">
         <v>3558006.51</v>
       </c>
-      <c r="T10" s="23">
+      <c r="T10" s="22">
         <v>3551101.42</v>
       </c>
-      <c r="U10" s="23">
+      <c r="U10" s="22">
         <v>3556368.66</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="str">
+      <c r="A11" s="21" t="str">
         <f>gurobi!A11</f>
         <v>(300, 140, 170, 5)</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="22">
         <v>1005.17</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="22">
         <v>981.98</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="22">
         <v>998.44</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="22">
         <v>742.47</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="22">
         <v>662.72</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="22">
         <v>893.41</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="22">
         <v>708.98</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="22">
         <v>693.11</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="22">
         <v>642.03</v>
       </c>
-      <c r="K11" s="23">
+      <c r="K11" s="22">
         <v>647.38</v>
       </c>
-      <c r="L11" s="23">
+      <c r="L11" s="22">
         <v>4353268.5199999996</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="22">
         <v>4355187.34</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N11" s="22">
         <v>4389938.68</v>
       </c>
-      <c r="O11" s="23">
+      <c r="O11" s="22">
         <v>4361796.1100000003</v>
       </c>
-      <c r="P11" s="23">
+      <c r="P11" s="22">
         <v>4335532.8099999996</v>
       </c>
-      <c r="Q11" s="23">
+      <c r="Q11" s="22">
         <v>4357849.16</v>
       </c>
-      <c r="R11" s="23">
+      <c r="R11" s="22">
         <v>4332611.38</v>
       </c>
-      <c r="S11" s="23">
+      <c r="S11" s="22">
         <v>4339404.33</v>
       </c>
-      <c r="T11" s="23">
+      <c r="T11" s="22">
         <v>4332938.38</v>
       </c>
-      <c r="U11" s="23">
+      <c r="U11" s="22">
         <v>4342522.51</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="str">
+      <c r="A12" s="21" t="str">
         <f>gurobi!A12</f>
         <v>(400, 150, 170 ,6)</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="22">
         <v>1031.8900000000001</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="22">
         <v>979.12</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="22">
         <v>985.27</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="22">
         <v>938.78</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="22">
         <v>970.75</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="22">
         <v>858.31</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="22">
         <v>870.95</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="22">
         <v>990.89</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="22">
         <v>929.88</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="22">
         <v>1002.77</v>
       </c>
-      <c r="L12" s="23">
+      <c r="L12" s="22">
         <v>5650331.3399999999</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="22">
         <v>5682884.04</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="22">
         <v>5643846.0700000003</v>
       </c>
-      <c r="O12" s="23">
+      <c r="O12" s="22">
         <v>5655649.6299999999</v>
       </c>
-      <c r="P12" s="23">
+      <c r="P12" s="22">
         <v>5670432.9400000004</v>
       </c>
-      <c r="Q12" s="23">
+      <c r="Q12" s="22">
         <v>5692777.2300000004</v>
       </c>
-      <c r="R12" s="23">
+      <c r="R12" s="22">
         <v>5669832.8200000003</v>
       </c>
-      <c r="S12" s="23">
+      <c r="S12" s="22">
         <v>5671566.4900000002</v>
       </c>
-      <c r="T12" s="23">
+      <c r="T12" s="22">
         <v>5676880.3200000003</v>
       </c>
-      <c r="U12" s="23">
+      <c r="U12" s="22">
         <v>5650402.0999999996</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="str">
+      <c r="A13" s="21" t="str">
         <f>gurobi!A13</f>
         <v>(600, 150, 200, 6)</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="U13" s="24"/>
+      <c r="B13" s="2">
+        <v>1701.52</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1643.47</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1702.97</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1850.23</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1737.38</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1787.83</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1869.59</v>
+      </c>
+      <c r="I13" s="2">
+        <v>2659.97</v>
+      </c>
+      <c r="J13" s="2">
+        <v>2210.9699999999998</v>
+      </c>
+      <c r="K13" s="13">
+        <v>1746.69</v>
+      </c>
+      <c r="L13" s="2">
+        <v>6172440.1699999999</v>
+      </c>
+      <c r="M13" s="2">
+        <v>6194876.1900000004</v>
+      </c>
+      <c r="N13" s="2">
+        <v>6175554.46</v>
+      </c>
+      <c r="O13" s="2">
+        <v>6172118.75</v>
+      </c>
+      <c r="P13" s="2">
+        <v>6164636.3600000003</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>6189842.0999999996</v>
+      </c>
+      <c r="R13" s="2">
+        <v>6184008.4000000004</v>
+      </c>
+      <c r="S13" s="2">
+        <v>6198492.9299999997</v>
+      </c>
+      <c r="T13" s="2">
+        <v>6163285.0099999998</v>
+      </c>
+      <c r="U13" s="13">
+        <v>6194580.6500000004</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4624,857 +4220,857 @@
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="23" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="25" t="s">
+      <c r="R1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="S1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="25" t="s">
+      <c r="T1" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="26" t="s">
+      <c r="U1" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="str">
+      <c r="A2" s="12" t="str">
         <f>gurobi!A2</f>
         <v>(2, 2, 4, 1)</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="26">
         <v>0.05</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="26">
         <v>0.02</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="26">
         <v>0.03</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="26">
         <v>0.03</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="26">
         <v>0.03</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="26">
         <v>0.02</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="26">
         <v>0.02</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="26">
         <v>0.03</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="26">
         <v>0.02</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="26">
         <v>0.02</v>
       </c>
-      <c r="L2" s="28">
+      <c r="L2" s="26">
         <v>28554.02</v>
       </c>
-      <c r="M2" s="28">
+      <c r="M2" s="26">
         <v>28554.02</v>
       </c>
-      <c r="N2" s="28">
+      <c r="N2" s="26">
         <v>28554.02</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="26">
         <v>28554.02</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="26">
         <v>28554.02</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="26">
         <v>28554.02</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="26">
         <v>28554.02</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="26">
         <v>28554.02</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="26">
         <v>28554.02</v>
       </c>
-      <c r="U2" s="29">
+      <c r="U2" s="27">
         <v>28554.02</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="str">
+      <c r="A3" s="12" t="str">
         <f>gurobi!A3</f>
         <v>(5, 4, 10, 1)</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="26">
         <v>0.11</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="26">
         <v>0.11</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="26">
         <v>0.09</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="26">
         <v>0.09</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="26">
         <v>0.11</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="26">
         <v>0.09</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="26">
         <v>0.11</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="26">
         <v>0.09</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="26">
         <v>0.11</v>
       </c>
-      <c r="K3" s="28">
+      <c r="K3" s="26">
         <v>0.12</v>
       </c>
-      <c r="L3" s="28">
+      <c r="L3" s="26">
         <v>61406.22</v>
       </c>
-      <c r="M3" s="28">
+      <c r="M3" s="26">
         <v>61403.82</v>
       </c>
-      <c r="N3" s="28">
+      <c r="N3" s="26">
         <v>61405.36</v>
       </c>
-      <c r="O3" s="28">
+      <c r="O3" s="26">
         <v>61402.81</v>
       </c>
-      <c r="P3" s="28">
+      <c r="P3" s="26">
         <v>61404.51</v>
       </c>
-      <c r="Q3" s="28">
+      <c r="Q3" s="26">
         <v>61402.81</v>
       </c>
-      <c r="R3" s="28">
+      <c r="R3" s="26">
         <v>61403.82</v>
       </c>
-      <c r="S3" s="28">
+      <c r="S3" s="26">
         <v>61402.81</v>
       </c>
-      <c r="T3" s="28">
+      <c r="T3" s="26">
         <v>61403.82</v>
       </c>
-      <c r="U3" s="29">
+      <c r="U3" s="27">
         <v>61402.05</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="str">
+      <c r="A4" s="12" t="str">
         <f>gurobi!A4</f>
         <v>(10, 8, 20, 2)</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="26">
         <v>0.52</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="26">
         <v>0.52</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="26">
         <v>0.53</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="26">
         <v>0.56000000000000005</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="26">
         <v>0.53</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="26">
         <v>0.53</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="26">
         <v>0.55000000000000004</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="26">
         <v>0.53</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="26">
         <v>0.52</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="26">
         <v>0.52</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="26">
         <v>192827.89</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="26">
         <v>192920.38</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="26">
         <v>192822.77</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="26">
         <v>193089.09</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="26">
         <v>193079.39</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="26">
         <v>193082.02</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="26">
         <v>192872.82</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="26">
         <v>192940.93</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="26">
         <v>192891.79</v>
       </c>
-      <c r="U4" s="29">
+      <c r="U4" s="27">
         <v>193280.45</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="str">
+      <c r="A5" s="12" t="str">
         <f>gurobi!A5</f>
-        <v>(15, 20, 30, 1)</v>
-      </c>
-      <c r="B5" s="28">
+        <v>(20, 20, 30, 2)</v>
+      </c>
+      <c r="B5" s="26">
         <v>2.17</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="26">
         <v>2.2200000000000002</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="26">
         <v>4.58</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="26">
         <v>2.19</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="26">
         <v>2.17</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="26">
         <v>2.17</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="26">
         <v>2.23</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="26">
         <v>6.91</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="26">
         <v>7</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="26">
         <v>2.33</v>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="26">
         <v>291872.90000000002</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="26">
         <v>291550.33</v>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="26">
         <v>291501.92</v>
       </c>
-      <c r="O5" s="28">
+      <c r="O5" s="26">
         <v>291672.67</v>
       </c>
-      <c r="P5" s="28">
+      <c r="P5" s="26">
         <v>292371.68</v>
       </c>
-      <c r="Q5" s="28">
+      <c r="Q5" s="26">
         <v>291194.59999999998</v>
       </c>
-      <c r="R5" s="28">
+      <c r="R5" s="26">
         <v>290969.65000000002</v>
       </c>
-      <c r="S5" s="28">
+      <c r="S5" s="26">
         <v>291742.31</v>
       </c>
-      <c r="T5" s="28">
+      <c r="T5" s="26">
         <v>291554.65000000002</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="27">
         <v>291268.03000000003</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="str">
+      <c r="A6" s="12" t="str">
         <f>gurobi!A6</f>
-        <v>(25, 50, 70, 2)</v>
-      </c>
-      <c r="B6" s="28">
+        <v>(50, 80, 70, 3)</v>
+      </c>
+      <c r="B6" s="26">
         <v>38.25</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="26">
         <v>25.12</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="26">
         <v>25.22</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="26">
         <v>24.8</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="26">
         <v>25.59</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="26">
         <v>26.2</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="26">
         <v>24.38</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="26">
         <v>24.78</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="26">
         <v>24.2</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="26">
         <v>24.42</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="26">
         <v>710310.9</v>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="26">
         <v>711000.34</v>
       </c>
-      <c r="N6" s="28">
+      <c r="N6" s="26">
         <v>711185.82</v>
       </c>
-      <c r="O6" s="28">
+      <c r="O6" s="26">
         <v>710495.32</v>
       </c>
-      <c r="P6" s="28">
+      <c r="P6" s="26">
         <v>711088.82</v>
       </c>
-      <c r="Q6" s="28">
+      <c r="Q6" s="26">
         <v>711294.09</v>
       </c>
-      <c r="R6" s="28">
+      <c r="R6" s="26">
         <v>711282.41</v>
       </c>
-      <c r="S6" s="28">
+      <c r="S6" s="26">
         <v>710894.55</v>
       </c>
-      <c r="T6" s="28">
+      <c r="T6" s="26">
         <v>710713.08</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="27">
         <v>712478.95</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="str">
+      <c r="A7" s="12" t="str">
         <f>gurobi!A7</f>
         <v>(70, 120, 100, 3)</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="26">
         <v>62.92</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="26">
         <v>64.78</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="26">
         <v>61.88</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="26">
         <v>61.61</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="26">
         <v>61.53</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="26">
         <v>99.86</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="26">
         <v>120.7</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="26">
         <v>145.62</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="26">
         <v>83.55</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="26">
         <v>62.52</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="26">
         <v>1376228.47</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="26">
         <v>1375244.47</v>
       </c>
-      <c r="N7" s="28">
+      <c r="N7" s="26">
         <v>1374479.05</v>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="26">
         <v>1374972.52</v>
       </c>
-      <c r="P7" s="28">
+      <c r="P7" s="26">
         <v>1375252.63</v>
       </c>
-      <c r="Q7" s="28">
+      <c r="Q7" s="26">
         <v>1375510.71</v>
       </c>
-      <c r="R7" s="28">
+      <c r="R7" s="26">
         <v>1376427.39</v>
       </c>
-      <c r="S7" s="28">
+      <c r="S7" s="26">
         <v>1374828.11</v>
       </c>
-      <c r="T7" s="28">
+      <c r="T7" s="26">
         <v>1376446.37</v>
       </c>
-      <c r="U7" s="29">
+      <c r="U7" s="27">
         <v>1375053.21</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="str">
+      <c r="A8" s="12" t="str">
         <f>gurobi!A8</f>
         <v>(100, 120, 100, 4)</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="26">
         <v>135.66999999999999</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="26">
         <v>127.62</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="26">
         <v>232.47</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="26">
         <v>213.19</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="26">
         <v>82.38</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="26">
         <v>80.73</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="26">
         <v>80.92</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="26">
         <v>80.83</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="26">
         <v>83.14</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="26">
         <v>81.73</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="26">
         <v>1908563.57</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="26">
         <v>1911241.06</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="26">
         <v>1909356.99</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="26">
         <v>1908683.41</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="26">
         <v>1909337.68</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="26">
         <v>1909915.62</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="26">
         <v>1908270.31</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="26">
         <v>1908663.63</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="26">
         <v>1910737.5</v>
       </c>
-      <c r="U8" s="29">
+      <c r="U8" s="27">
         <v>1909408.89</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="str">
+      <c r="A9" s="12" t="str">
         <f>gurobi!A9</f>
         <v>(150, 120, 130, 4)</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="26">
         <v>151.94999999999999</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="26">
         <v>151.97999999999999</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="26">
         <v>151.31</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="26">
         <v>150.41</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="26">
         <v>151.16999999999999</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="26">
         <v>155.27000000000001</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="26">
         <v>154.19999999999999</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="26">
         <v>153.38999999999999</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="26">
         <v>154.22</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="26">
         <v>154.38</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="26">
         <v>2232368.64</v>
       </c>
-      <c r="M9" s="28">
+      <c r="M9" s="26">
         <v>2233822.29</v>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="26">
         <v>2231980.5699999998</v>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="26">
         <v>2232887.75</v>
       </c>
-      <c r="P9" s="28">
+      <c r="P9" s="26">
         <v>2231551.1800000002</v>
       </c>
-      <c r="Q9" s="28">
+      <c r="Q9" s="26">
         <v>2232420.9</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="26">
         <v>2232126.71</v>
       </c>
-      <c r="S9" s="28">
+      <c r="S9" s="26">
         <v>2232148.21</v>
       </c>
-      <c r="T9" s="28">
+      <c r="T9" s="26">
         <v>2232439.37</v>
       </c>
-      <c r="U9" s="29">
+      <c r="U9" s="27">
         <v>2231096.2400000002</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="str">
+      <c r="A10" s="12" t="str">
         <f>gurobi!A10</f>
         <v>(200, 130, 150, 5)</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="26">
         <v>290.77999999999997</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="26">
         <v>294.47000000000003</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="26">
         <v>292.38</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="26">
         <v>293.91000000000003</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="26">
         <v>294.91000000000003</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="26">
         <v>291.83</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="26">
         <v>290.75</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="26">
         <v>290.16000000000003</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="26">
         <v>289.27</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="26">
         <v>296.42</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="26">
         <v>3528029.43</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="26">
         <v>3529834.73</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="26">
         <v>3526931.45</v>
       </c>
-      <c r="O10" s="28">
+      <c r="O10" s="26">
         <v>3528504.63</v>
       </c>
-      <c r="P10" s="28">
+      <c r="P10" s="26">
         <v>3528163.47</v>
       </c>
-      <c r="Q10" s="28">
+      <c r="Q10" s="26">
         <v>3528587.12</v>
       </c>
-      <c r="R10" s="28">
+      <c r="R10" s="26">
         <v>3529244</v>
       </c>
-      <c r="S10" s="28">
+      <c r="S10" s="26">
         <v>3528285.98</v>
       </c>
-      <c r="T10" s="28">
+      <c r="T10" s="26">
         <v>3528582.12</v>
       </c>
-      <c r="U10" s="29">
+      <c r="U10" s="27">
         <v>3527688.92</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="str">
+      <c r="A11" s="12" t="str">
         <f>gurobi!A11</f>
         <v>(300, 140, 170, 5)</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="26">
         <v>821.58</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="26">
         <v>816.38</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="26">
         <v>814.66</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="26">
         <v>818.33</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="26">
         <v>538.53</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="26">
         <v>546.78</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="26">
         <v>539.75</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="26">
         <v>534.23</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="26">
         <v>537.73</v>
       </c>
-      <c r="K11" s="28">
+      <c r="K11" s="26">
         <v>529</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="26">
         <v>4300944.72</v>
       </c>
-      <c r="M11" s="28">
+      <c r="M11" s="26">
         <v>4297507.59</v>
       </c>
-      <c r="N11" s="28">
+      <c r="N11" s="26">
         <v>4301321.07</v>
       </c>
-      <c r="O11" s="28">
+      <c r="O11" s="26">
         <v>4296734.46</v>
       </c>
-      <c r="P11" s="28">
+      <c r="P11" s="26">
         <v>4300362.12</v>
       </c>
-      <c r="Q11" s="28">
+      <c r="Q11" s="26">
         <v>4299926.3600000003</v>
       </c>
-      <c r="R11" s="28">
+      <c r="R11" s="26">
         <v>4296711.09</v>
       </c>
-      <c r="S11" s="28">
+      <c r="S11" s="26">
         <v>4298111.21</v>
       </c>
-      <c r="T11" s="28">
+      <c r="T11" s="26">
         <v>4299310.53</v>
       </c>
-      <c r="U11" s="29">
+      <c r="U11" s="27">
         <v>4297808.95</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="str">
+      <c r="A12" s="12" t="str">
         <f>gurobi!A12</f>
         <v>(400, 150, 170 ,6)</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="26">
         <v>698.11</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="26">
         <v>690.62</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="26">
         <v>696.61</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="26">
         <v>692.83</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="26">
         <v>734.61</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="26">
         <v>696.02</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="26">
         <v>705.69</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="26">
         <v>691.75</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="26">
         <v>697.47</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="26">
         <v>709.72</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="26">
         <v>5606088.0899999999</v>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="26">
         <v>5606656.71</v>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="26">
         <v>5607396.4199999999</v>
       </c>
-      <c r="O12" s="28">
+      <c r="O12" s="26">
         <v>5607549.9199999999</v>
       </c>
-      <c r="P12" s="28">
+      <c r="P12" s="26">
         <v>5604781.6799999997</v>
       </c>
-      <c r="Q12" s="28">
+      <c r="Q12" s="26">
         <v>5611496.6100000003</v>
       </c>
-      <c r="R12" s="28">
+      <c r="R12" s="26">
         <v>5603946.7699999996</v>
       </c>
-      <c r="S12" s="28">
+      <c r="S12" s="26">
         <v>5606391.2699999996</v>
       </c>
-      <c r="T12" s="28">
+      <c r="T12" s="26">
         <v>5611442.3200000003</v>
       </c>
-      <c r="U12" s="29">
+      <c r="U12" s="27">
         <v>5605726.2300000004</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="str">
+      <c r="A13" s="25" t="str">
         <f>gurobi!A13</f>
         <v>(600, 150, 200, 6)</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>222</v>
+        <v>138</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>224</v>
+        <v>140</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>226</v>
+        <v>142</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>228</v>
+        <v>144</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>230</v>
+        <v>146</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>232</v>
+        <v>148</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>236</v>
+        <v>152</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>219</v>
+        <v>135</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>221</v>
+        <v>137</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>223</v>
+        <v>139</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>225</v>
+        <v>141</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>227</v>
+        <v>143</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>229</v>
+        <v>145</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>231</v>
+        <v>147</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>233</v>
+        <v>149</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>235</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -5507,857 +5103,857 @@
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="23" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="25" t="s">
+      <c r="R1" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="S1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="25" t="s">
+      <c r="T1" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="26" t="s">
+      <c r="U1" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="str">
+      <c r="A2" s="12" t="str">
         <f>gurobi!A2</f>
         <v>(2, 2, 4, 1)</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="J2" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="L2" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="M2" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="O2" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="P2" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="R2" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="S2" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="T2" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="U2" s="29" t="s">
-        <v>135</v>
+      <c r="B2" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="P2" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="T2" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="U2" s="27" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="str">
+      <c r="A3" s="12" t="str">
         <f>gurobi!A3</f>
         <v>(5, 4, 10, 1)</v>
       </c>
-      <c r="B3" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="J3" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="M3" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="N3" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="O3" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="P3" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q3" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="R3" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="S3" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="T3" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="U3" s="29" t="s">
-        <v>140</v>
+      <c r="B3" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="R3" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="S3" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="T3" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" s="27" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="str">
+      <c r="A4" s="12" t="str">
         <f>gurobi!A4</f>
         <v>(10, 8, 20, 2)</v>
       </c>
-      <c r="B4" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="M4" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="N4" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="O4" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="P4" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q4" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="R4" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="S4" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="T4" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="U4" s="29" t="s">
-        <v>150</v>
+      <c r="B4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q4" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="R4" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="S4" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="T4" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="U4" s="27" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="str">
+      <c r="A5" s="12" t="str">
         <f>gurobi!A5</f>
-        <v>(15, 20, 30, 1)</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="K5" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="L5" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="M5" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="N5" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="O5" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="P5" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q5" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="R5" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="S5" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="T5" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="U5" s="29" t="s">
-        <v>174</v>
+        <v>(20, 20, 30, 2)</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="P5" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q5" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="R5" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="S5" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="T5" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="U5" s="27" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="str">
+      <c r="A6" s="12" t="str">
         <f>gurobi!A6</f>
-        <v>(25, 50, 70, 2)</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="K6" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="L6" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="N6" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="O6" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="P6" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q6" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="R6" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="S6" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="T6" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="U6" s="29" t="s">
-        <v>194</v>
+        <v>(50, 80, 70, 3)</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="N6" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="P6" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="R6" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="S6" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="U6" s="27" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="str">
+      <c r="A7" s="12" t="str">
         <f>gurobi!A7</f>
         <v>(70, 120, 100, 3)</v>
       </c>
-      <c r="B7" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="K7" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="L7" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="N7" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q7" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="R7" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="S7" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="T7" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="U7" s="29" t="s">
-        <v>71</v>
+      <c r="B7" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="R7" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="S7" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="T7" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="U7" s="27" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="str">
+      <c r="A8" s="12" t="str">
         <f>gurobi!A8</f>
         <v>(100, 120, 100, 4)</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="28">
         <v>51.73</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="28">
         <v>45.08</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="28">
         <v>46.94</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="28">
         <v>97.31</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="28">
         <v>30.77</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="28">
         <v>30.72</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="28">
         <v>30.53</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="28">
         <v>30.62</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="28">
         <v>30.92</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="28">
         <v>30.86</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="28">
         <v>1912381.4</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="28">
         <v>1909337.65</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="28">
         <v>1910216.71</v>
       </c>
-      <c r="O8" s="30">
+      <c r="O8" s="28">
         <v>1909845.04</v>
       </c>
-      <c r="P8" s="30">
+      <c r="P8" s="28">
         <v>1909073.79</v>
       </c>
-      <c r="Q8" s="30">
+      <c r="Q8" s="28">
         <v>1908701.36</v>
       </c>
-      <c r="R8" s="30">
+      <c r="R8" s="28">
         <v>1909092.16</v>
       </c>
-      <c r="S8" s="30">
+      <c r="S8" s="28">
         <v>1909253.3</v>
       </c>
-      <c r="T8" s="30">
+      <c r="T8" s="28">
         <v>1908625.58</v>
       </c>
-      <c r="U8" s="31">
+      <c r="U8" s="29">
         <v>1910893.46</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="str">
+      <c r="A9" s="12" t="str">
         <f>gurobi!A9</f>
         <v>(150, 120, 130, 4)</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="28">
         <v>44.19</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="28">
         <v>40.549999999999997</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="28">
         <v>40.380000000000003</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="28">
         <v>39.880000000000003</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="28">
         <v>39.799999999999997</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="28">
         <v>39.44</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="28">
         <v>40.22</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="28">
         <v>39.39</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="28">
         <v>40.049999999999997</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="28">
         <v>39.89</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="28">
         <v>2231805.37</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="28">
         <v>2230661.9500000002</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="28">
         <v>2231344.37</v>
       </c>
-      <c r="O9" s="30">
+      <c r="O9" s="28">
         <v>2230605.7799999998</v>
       </c>
-      <c r="P9" s="30">
+      <c r="P9" s="28">
         <v>2232022.42</v>
       </c>
-      <c r="Q9" s="30">
+      <c r="Q9" s="28">
         <v>2230767.42</v>
       </c>
-      <c r="R9" s="30">
+      <c r="R9" s="28">
         <v>2231271.79</v>
       </c>
-      <c r="S9" s="30">
+      <c r="S9" s="28">
         <v>2230880.5499999998</v>
       </c>
-      <c r="T9" s="30">
+      <c r="T9" s="28">
         <v>2231863.59</v>
       </c>
-      <c r="U9" s="31">
+      <c r="U9" s="29">
         <v>2231322.2999999998</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="str">
+      <c r="A10" s="12" t="str">
         <f>gurobi!A10</f>
         <v>(200, 130, 150, 5)</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="28">
         <v>61.45</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="28">
         <v>60.11</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="28">
         <v>59.92</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="28">
         <v>59.84</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="28">
         <v>60.17</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="28">
         <v>59.69</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="28">
         <v>65.84</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="28">
         <v>65.03</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="28">
         <v>64.69</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="28">
         <v>65.34</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="28">
         <v>3527865.49</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M10" s="28">
         <v>3539052.73</v>
       </c>
-      <c r="N10" s="30">
+      <c r="N10" s="28">
         <v>3531391.43</v>
       </c>
-      <c r="O10" s="30">
+      <c r="O10" s="28">
         <v>3530455.32</v>
       </c>
-      <c r="P10" s="30">
+      <c r="P10" s="28">
         <v>3534073.66</v>
       </c>
-      <c r="Q10" s="30">
+      <c r="Q10" s="28">
         <v>3537746.29</v>
       </c>
-      <c r="R10" s="30">
+      <c r="R10" s="28">
         <v>3529434.82</v>
       </c>
-      <c r="S10" s="30">
+      <c r="S10" s="28">
         <v>3529762.36</v>
       </c>
-      <c r="T10" s="30">
+      <c r="T10" s="28">
         <v>3529912.01</v>
       </c>
-      <c r="U10" s="31">
+      <c r="U10" s="29">
         <v>3531222.69</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="str">
+      <c r="A11" s="12" t="str">
         <f>gurobi!A11</f>
         <v>(300, 140, 170, 5)</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="28">
         <v>130.81</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="28">
         <v>122.12</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="28">
         <v>121.25</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="28">
         <v>120.88</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="28">
         <v>87.89</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="28">
         <v>82.94</v>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="28">
         <v>85.03</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="28">
         <v>93.78</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="28">
         <v>92.91</v>
       </c>
-      <c r="K11" s="30">
+      <c r="K11" s="28">
         <v>93.14</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="28">
         <v>4297373.66</v>
       </c>
-      <c r="M11" s="30">
+      <c r="M11" s="28">
         <v>4304351.01</v>
       </c>
-      <c r="N11" s="30">
+      <c r="N11" s="28">
         <v>4304498.22</v>
       </c>
-      <c r="O11" s="30">
+      <c r="O11" s="28">
         <v>4326442.3</v>
       </c>
-      <c r="P11" s="30">
+      <c r="P11" s="28">
         <v>4301066.4800000004</v>
       </c>
-      <c r="Q11" s="30">
+      <c r="Q11" s="28">
         <v>4304770.08</v>
       </c>
-      <c r="R11" s="30">
+      <c r="R11" s="28">
         <v>4305921.2</v>
       </c>
-      <c r="S11" s="30">
+      <c r="S11" s="28">
         <v>4299799.3499999996</v>
       </c>
-      <c r="T11" s="30">
+      <c r="T11" s="28">
         <v>4297695.41</v>
       </c>
-      <c r="U11" s="31">
+      <c r="U11" s="29">
         <v>4298625.42</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="str">
+      <c r="A12" s="12" t="str">
         <f>gurobi!A12</f>
         <v>(400, 150, 170 ,6)</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="28">
         <v>196.25</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="28">
         <v>115.34</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="28">
         <v>111.19</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="28">
         <v>112.31</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="28">
         <v>130.78</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="28">
         <v>112.22</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="28">
         <v>112.09</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="28">
         <v>113.3</v>
       </c>
-      <c r="J12" s="30">
+      <c r="J12" s="28">
         <v>113.25</v>
       </c>
-      <c r="K12" s="30">
+      <c r="K12" s="28">
         <v>111.84</v>
       </c>
-      <c r="L12" s="30">
+      <c r="L12" s="28">
         <v>5605158.3200000003</v>
       </c>
-      <c r="M12" s="30">
+      <c r="M12" s="28">
         <v>5605168.5700000003</v>
       </c>
-      <c r="N12" s="30">
+      <c r="N12" s="28">
         <v>5616125.21</v>
       </c>
-      <c r="O12" s="30">
+      <c r="O12" s="28">
         <v>5608806.2699999996</v>
       </c>
-      <c r="P12" s="30">
+      <c r="P12" s="28">
         <v>5608678.4000000004</v>
       </c>
-      <c r="Q12" s="30">
+      <c r="Q12" s="28">
         <v>5607460.4299999997</v>
       </c>
-      <c r="R12" s="30">
+      <c r="R12" s="28">
         <v>5610159.6600000001</v>
       </c>
-      <c r="S12" s="30">
+      <c r="S12" s="28">
         <v>5603535.4100000001</v>
       </c>
-      <c r="T12" s="30">
+      <c r="T12" s="28">
         <v>5604137.46</v>
       </c>
-      <c r="U12" s="31">
+      <c r="U12" s="29">
         <v>5606175.3600000003</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="str">
+      <c r="A13" s="25" t="str">
         <f>gurobi!A13</f>
         <v>(600, 150, 200, 6)</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>198</v>
+        <v>114</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>200</v>
+        <v>116</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>204</v>
+        <v>120</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>206</v>
+        <v>122</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>208</v>
+        <v>124</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>214</v>
+        <v>130</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>197</v>
+        <v>113</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>199</v>
+        <v>115</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>201</v>
+        <v>117</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>203</v>
+        <v>119</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>205</v>
+        <v>121</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>207</v>
+        <v>123</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>209</v>
+        <v>125</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>211</v>
+        <v>127</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>213</v>
+        <v>129</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>215</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
